--- a/Book.xlsx
+++ b/Book.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kilosort\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kilosort\Documents\GitHub\mouse-duty-scheduler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{234ADC66-607A-40B5-9D8A-E413B4D074E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7379863E-5C08-436E-9A18-0E31BC4243A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{EF67FB10-9A92-4FD7-B7AE-E2E207162E6D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF67FB10-9A92-4FD7-B7AE-E2E207162E6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,25 +80,25 @@
     <t>Surgery Date</t>
   </si>
   <si>
-    <t>ABR Baseline 1 Date (-3)</t>
-  </si>
-  <si>
-    <t>ABR Baseline 2 Date (-1)</t>
-  </si>
-  <si>
-    <t>Exposed ABR1 Date (+1)</t>
-  </si>
-  <si>
-    <t>Exposed ABR 2 Date (+3)</t>
-  </si>
-  <si>
-    <t>Exposed ABR3 Date (+13)</t>
-  </si>
-  <si>
-    <t>Exposed ABR3 Date (+15)</t>
-  </si>
-  <si>
-    <t>NIHL Date (0)</t>
+    <t>ABR Baseline 1  (day -3)</t>
+  </si>
+  <si>
+    <t>ABR Baseline 2 (day -1)</t>
+  </si>
+  <si>
+    <t>NIHL (Day 0)</t>
+  </si>
+  <si>
+    <t>Exposed ABR1  (Day +1)</t>
+  </si>
+  <si>
+    <t>Exposed ABR 2  (Day +3)</t>
+  </si>
+  <si>
+    <t>Exposed ABR3  (Day +13)</t>
+  </si>
+  <si>
+    <t>Exposed ABR3 (Day +15)</t>
   </si>
 </sst>
 </file>
@@ -510,19 +510,19 @@
         <v>14</v>
       </c>
       <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
         <v>19</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">

--- a/Book.xlsx
+++ b/Book.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kilosort\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kilosort\Documents\GitHub\mouse-duty-scheduler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FBA3803-097B-442E-87B5-59825E5400A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEF1F91-9B36-494D-BED1-3119FC7607D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>NIHL / ABR Experimental Schedule</t>
   </si>
@@ -260,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -284,17 +284,14 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -302,15 +299,15 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -336,7 +333,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ABR Baseline 3_x000a_(day -2) - Left ear"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ABR Baseline 4_x000a_(day -1) - Right ear"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="NIHL_x000a_(Day 0)"/>
-    <tableColumn id="15" xr3:uid="{8DC5CB09-49CC-4F51-9A7D-2210E08202F5}" name="Sound Level" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{8DC5CB09-49CC-4F51-9A7D-2210E08202F5}" name="Sound Level" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Exposed ABR1_x000a_(Day +1) Left + Right ear"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Exposed ABR2_x000a_(Day +3) Left + Right ear"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Exposed ABR3 Left ear_x000a_(Day +13)"/>
@@ -498,7 +495,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -507,46 +504,46 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="28" customWidth="1"/>
     <col min="11" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="13.75" customWidth="1"/>
+    <col min="15" max="15" width="13.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27.95" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:15" ht="27.9" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-    </row>
-    <row r="4" spans="1:15" ht="45.95" customHeight="1">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+    </row>
+    <row r="4" spans="1:15" ht="45.9" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -571,7 +568,7 @@
       <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="9" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -619,34 +616,34 @@
         <v>46151</v>
       </c>
       <c r="H5" s="5">
-        <f t="shared" ref="H5:H14" si="3">IF($D5="","",$D5+4)</f>
-        <v>46152</v>
-      </c>
-      <c r="I5" s="12">
-        <v>103</v>
+        <f>IF($D5="","",$D5+5)</f>
+        <v>46153</v>
+      </c>
+      <c r="I5" s="4">
+        <v>106</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" ref="J5:J14" si="4">IF($D5="","",$D5+5)</f>
-        <v>46153</v>
+        <f>IF($D5="","",$D5+6)</f>
+        <v>46154</v>
       </c>
       <c r="K5" s="5">
-        <f t="shared" ref="K5:K14" si="5">IF($D5="","",$D5+7)</f>
+        <f t="shared" ref="K5:K14" si="3">IF($D5="","",$D5+7)</f>
         <v>46155</v>
       </c>
       <c r="L5" s="5">
-        <f t="shared" ref="L5:L14" si="6">IF($D5="","",$D5+17)</f>
+        <f t="shared" ref="L5:L14" si="4">IF($D5="","",$D5+17)</f>
         <v>46165</v>
       </c>
       <c r="M5" s="5">
-        <f t="shared" ref="M5:M14" si="7">IF($D5="","",$D5+18)</f>
+        <f t="shared" ref="M5:M14" si="5">IF($D5="","",$D5+18)</f>
         <v>46166</v>
       </c>
       <c r="N5" s="5">
-        <f t="shared" ref="N5:N14" si="8">IF($D5="","",$D5+19)</f>
+        <f t="shared" ref="N5:N14" si="6">IF($D5="","",$D5+19)</f>
         <v>46167</v>
       </c>
       <c r="O5" s="5">
-        <f t="shared" ref="O5:O14" si="9">IF($D5="","",$D5+20)</f>
+        <f t="shared" ref="O5:O14" si="7">IF($D5="","",$D5+20)</f>
         <v>46168</v>
       </c>
     </row>
@@ -676,34 +673,34 @@
         <v>46151</v>
       </c>
       <c r="H6" s="5">
+        <f>IF($D6="","",$D6+5)</f>
+        <v>46153</v>
+      </c>
+      <c r="I6" s="4">
+        <v>106</v>
+      </c>
+      <c r="J6" s="5">
+        <f>IF($D6="","",$D6+6)</f>
+        <v>46154</v>
+      </c>
+      <c r="K6" s="5">
         <f t="shared" si="3"/>
-        <v>46152</v>
-      </c>
-      <c r="I6" s="12">
-        <v>103</v>
-      </c>
-      <c r="J6" s="5">
+        <v>46155</v>
+      </c>
+      <c r="L6" s="5">
         <f t="shared" si="4"/>
-        <v>46153</v>
-      </c>
-      <c r="K6" s="5">
+        <v>46165</v>
+      </c>
+      <c r="M6" s="5">
         <f t="shared" si="5"/>
-        <v>46155</v>
-      </c>
-      <c r="L6" s="5">
+        <v>46166</v>
+      </c>
+      <c r="N6" s="5">
         <f t="shared" si="6"/>
-        <v>46165</v>
-      </c>
-      <c r="M6" s="5">
+        <v>46167</v>
+      </c>
+      <c r="O6" s="5">
         <f t="shared" si="7"/>
-        <v>46166</v>
-      </c>
-      <c r="N6" s="5">
-        <f t="shared" si="8"/>
-        <v>46167</v>
-      </c>
-      <c r="O6" s="5">
-        <f t="shared" si="9"/>
         <v>46168</v>
       </c>
     </row>
@@ -733,34 +730,34 @@
         <v>46152</v>
       </c>
       <c r="H7" s="5">
+        <f>IF($D7="","",$D7+5)</f>
+        <v>46154</v>
+      </c>
+      <c r="I7" s="4">
+        <v>106</v>
+      </c>
+      <c r="J7" s="5">
+        <f>IF($D7="","",$D7+6)</f>
+        <v>46155</v>
+      </c>
+      <c r="K7" s="5">
         <f t="shared" si="3"/>
-        <v>46153</v>
-      </c>
-      <c r="I7" s="12">
-        <v>104</v>
-      </c>
-      <c r="J7" s="5">
+        <v>46156</v>
+      </c>
+      <c r="L7" s="5">
         <f t="shared" si="4"/>
-        <v>46154</v>
-      </c>
-      <c r="K7" s="5">
+        <v>46166</v>
+      </c>
+      <c r="M7" s="5">
         <f t="shared" si="5"/>
-        <v>46156</v>
-      </c>
-      <c r="L7" s="5">
+        <v>46167</v>
+      </c>
+      <c r="N7" s="5">
         <f t="shared" si="6"/>
-        <v>46166</v>
-      </c>
-      <c r="M7" s="5">
+        <v>46168</v>
+      </c>
+      <c r="O7" s="5">
         <f t="shared" si="7"/>
-        <v>46167</v>
-      </c>
-      <c r="N7" s="5">
-        <f t="shared" si="8"/>
-        <v>46168</v>
-      </c>
-      <c r="O7" s="5">
-        <f t="shared" si="9"/>
         <v>46169</v>
       </c>
     </row>
@@ -790,34 +787,34 @@
         <v>46152</v>
       </c>
       <c r="H8" s="5">
+        <f>IF($D8="","",$D8+5)</f>
+        <v>46154</v>
+      </c>
+      <c r="I8" s="4">
+        <v>106</v>
+      </c>
+      <c r="J8" s="5">
+        <f>IF($D8="","",$D8+6)</f>
+        <v>46155</v>
+      </c>
+      <c r="K8" s="5">
         <f t="shared" si="3"/>
-        <v>46153</v>
-      </c>
-      <c r="I8" s="12">
-        <v>104</v>
-      </c>
-      <c r="J8" s="5">
+        <v>46156</v>
+      </c>
+      <c r="L8" s="5">
         <f t="shared" si="4"/>
-        <v>46154</v>
-      </c>
-      <c r="K8" s="5">
+        <v>46166</v>
+      </c>
+      <c r="M8" s="5">
         <f t="shared" si="5"/>
-        <v>46156</v>
-      </c>
-      <c r="L8" s="5">
+        <v>46167</v>
+      </c>
+      <c r="N8" s="5">
         <f t="shared" si="6"/>
-        <v>46166</v>
-      </c>
-      <c r="M8" s="5">
+        <v>46168</v>
+      </c>
+      <c r="O8" s="5">
         <f t="shared" si="7"/>
-        <v>46167</v>
-      </c>
-      <c r="N8" s="5">
-        <f t="shared" si="8"/>
-        <v>46168</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" si="9"/>
         <v>46169</v>
       </c>
     </row>
@@ -847,34 +844,34 @@
         <v>46159</v>
       </c>
       <c r="H9" s="5">
+        <f t="shared" ref="H5:H14" si="8">IF($D9="","",$D9+4)</f>
+        <v>46160</v>
+      </c>
+      <c r="I9" s="4">
+        <v>104</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" ref="J5:J14" si="9">IF($D9="","",$D9+5)</f>
+        <v>46161</v>
+      </c>
+      <c r="K9" s="5">
         <f t="shared" si="3"/>
-        <v>46160</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="5">
+        <v>46163</v>
+      </c>
+      <c r="L9" s="5">
         <f t="shared" si="4"/>
-        <v>46161</v>
-      </c>
-      <c r="K9" s="5">
+        <v>46173</v>
+      </c>
+      <c r="M9" s="5">
         <f t="shared" si="5"/>
-        <v>46163</v>
-      </c>
-      <c r="L9" s="5">
+        <v>46174</v>
+      </c>
+      <c r="N9" s="5">
         <f t="shared" si="6"/>
-        <v>46173</v>
-      </c>
-      <c r="M9" s="5">
+        <v>46175</v>
+      </c>
+      <c r="O9" s="5">
         <f t="shared" si="7"/>
-        <v>46174</v>
-      </c>
-      <c r="N9" s="5">
-        <f t="shared" si="8"/>
-        <v>46175</v>
-      </c>
-      <c r="O9" s="5">
-        <f t="shared" si="9"/>
         <v>46176</v>
       </c>
     </row>
@@ -904,34 +901,34 @@
         <v>46160</v>
       </c>
       <c r="H10" s="5">
+        <f t="shared" si="8"/>
+        <v>46161</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="9"/>
+        <v>46162</v>
+      </c>
+      <c r="K10" s="5">
         <f t="shared" si="3"/>
-        <v>46161</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="5">
+        <v>46164</v>
+      </c>
+      <c r="L10" s="5">
         <f t="shared" si="4"/>
-        <v>46162</v>
-      </c>
-      <c r="K10" s="5">
+        <v>46174</v>
+      </c>
+      <c r="M10" s="5">
         <f t="shared" si="5"/>
-        <v>46164</v>
-      </c>
-      <c r="L10" s="5">
+        <v>46175</v>
+      </c>
+      <c r="N10" s="5">
         <f t="shared" si="6"/>
-        <v>46174</v>
-      </c>
-      <c r="M10" s="5">
+        <v>46176</v>
+      </c>
+      <c r="O10" s="5">
         <f t="shared" si="7"/>
-        <v>46175</v>
-      </c>
-      <c r="N10" s="5">
-        <f t="shared" si="8"/>
-        <v>46176</v>
-      </c>
-      <c r="O10" s="5">
-        <f t="shared" si="9"/>
         <v>46177</v>
       </c>
     </row>
@@ -961,34 +958,34 @@
         <v>46163</v>
       </c>
       <c r="H11" s="5">
+        <f t="shared" si="8"/>
+        <v>46164</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="9"/>
+        <v>46165</v>
+      </c>
+      <c r="K11" s="5">
         <f t="shared" si="3"/>
-        <v>46164</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="5">
+        <v>46167</v>
+      </c>
+      <c r="L11" s="5">
         <f t="shared" si="4"/>
-        <v>46165</v>
-      </c>
-      <c r="K11" s="5">
+        <v>46177</v>
+      </c>
+      <c r="M11" s="5">
         <f t="shared" si="5"/>
-        <v>46167</v>
-      </c>
-      <c r="L11" s="5">
+        <v>46178</v>
+      </c>
+      <c r="N11" s="5">
         <f t="shared" si="6"/>
-        <v>46177</v>
-      </c>
-      <c r="M11" s="5">
+        <v>46179</v>
+      </c>
+      <c r="O11" s="5">
         <f t="shared" si="7"/>
-        <v>46178</v>
-      </c>
-      <c r="N11" s="5">
-        <f t="shared" si="8"/>
-        <v>46179</v>
-      </c>
-      <c r="O11" s="5">
-        <f t="shared" si="9"/>
         <v>46180</v>
       </c>
     </row>
@@ -1018,34 +1015,34 @@
         <v>46164</v>
       </c>
       <c r="H12" s="5">
+        <f t="shared" si="8"/>
+        <v>46165</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="9"/>
+        <v>46166</v>
+      </c>
+      <c r="K12" s="5">
         <f t="shared" si="3"/>
-        <v>46165</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="5">
+        <v>46168</v>
+      </c>
+      <c r="L12" s="5">
         <f t="shared" si="4"/>
-        <v>46166</v>
-      </c>
-      <c r="K12" s="5">
+        <v>46178</v>
+      </c>
+      <c r="M12" s="5">
         <f t="shared" si="5"/>
-        <v>46168</v>
-      </c>
-      <c r="L12" s="5">
+        <v>46179</v>
+      </c>
+      <c r="N12" s="5">
         <f t="shared" si="6"/>
-        <v>46178</v>
-      </c>
-      <c r="M12" s="5">
+        <v>46180</v>
+      </c>
+      <c r="O12" s="5">
         <f t="shared" si="7"/>
-        <v>46179</v>
-      </c>
-      <c r="N12" s="5">
-        <f t="shared" si="8"/>
-        <v>46180</v>
-      </c>
-      <c r="O12" s="5">
-        <f t="shared" si="9"/>
         <v>46181</v>
       </c>
     </row>
@@ -1075,34 +1072,34 @@
         <v>46164</v>
       </c>
       <c r="H13" s="5">
+        <f t="shared" si="8"/>
+        <v>46165</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="9"/>
+        <v>46166</v>
+      </c>
+      <c r="K13" s="5">
         <f t="shared" si="3"/>
-        <v>46165</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="5">
+        <v>46168</v>
+      </c>
+      <c r="L13" s="5">
         <f t="shared" si="4"/>
-        <v>46166</v>
-      </c>
-      <c r="K13" s="5">
+        <v>46178</v>
+      </c>
+      <c r="M13" s="5">
         <f t="shared" si="5"/>
-        <v>46168</v>
-      </c>
-      <c r="L13" s="5">
+        <v>46179</v>
+      </c>
+      <c r="N13" s="5">
         <f t="shared" si="6"/>
-        <v>46178</v>
-      </c>
-      <c r="M13" s="5">
+        <v>46180</v>
+      </c>
+      <c r="O13" s="5">
         <f t="shared" si="7"/>
-        <v>46179</v>
-      </c>
-      <c r="N13" s="5">
-        <f t="shared" si="8"/>
-        <v>46180</v>
-      </c>
-      <c r="O13" s="5">
-        <f t="shared" si="9"/>
         <v>46181</v>
       </c>
     </row>
@@ -1132,38 +1129,38 @@
         <v>46172</v>
       </c>
       <c r="H14" s="5">
+        <f t="shared" si="8"/>
+        <v>46173</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="9"/>
+        <v>46174</v>
+      </c>
+      <c r="K14" s="5">
         <f t="shared" si="3"/>
-        <v>46173</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="5">
+        <v>46176</v>
+      </c>
+      <c r="L14" s="5">
         <f t="shared" si="4"/>
-        <v>46174</v>
-      </c>
-      <c r="K14" s="5">
+        <v>46186</v>
+      </c>
+      <c r="M14" s="5">
         <f t="shared" si="5"/>
-        <v>46176</v>
-      </c>
-      <c r="L14" s="5">
+        <v>46187</v>
+      </c>
+      <c r="N14" s="5">
         <f t="shared" si="6"/>
-        <v>46186</v>
-      </c>
-      <c r="M14" s="5">
+        <v>46188</v>
+      </c>
+      <c r="O14" s="5">
         <f t="shared" si="7"/>
-        <v>46187</v>
-      </c>
-      <c r="N14" s="5">
-        <f t="shared" si="8"/>
-        <v>46188</v>
-      </c>
-      <c r="O14" s="5">
-        <f t="shared" si="9"/>
         <v>46189</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15">
+    <row r="17" spans="1:9">
       <c r="A17" s="8" t="s">
         <v>21</v>
       </c>
@@ -1373,7 +1370,7 @@
     <mergeCell ref="A2:N2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:O14">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>WEEKDAY(B5,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Book.xlsx
+++ b/Book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kilosort\Documents\GitHub\mouse-duty-scheduler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEF1F91-9B36-494D-BED1-3119FC7607D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6314D9-01F4-40DD-9B29-646E139FE919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -677,7 +677,7 @@
         <v>46153</v>
       </c>
       <c r="I6" s="4">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="J6" s="5">
         <f>IF($D6="","",$D6+6)</f>
@@ -791,7 +791,7 @@
         <v>46154</v>
       </c>
       <c r="I8" s="4">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="J8" s="5">
         <f>IF($D8="","",$D8+6)</f>
@@ -844,14 +844,14 @@
         <v>46159</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" ref="H5:H14" si="8">IF($D9="","",$D9+4)</f>
+        <f t="shared" ref="H9:H14" si="8">IF($D9="","",$D9+4)</f>
         <v>46160</v>
       </c>
       <c r="I9" s="4">
         <v>104</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J5:J14" si="9">IF($D9="","",$D9+5)</f>
+        <f t="shared" ref="J9:J14" si="9">IF($D9="","",$D9+5)</f>
         <v>46161</v>
       </c>
       <c r="K9" s="5">
